--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486551_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486551_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.657299999999999</v>
+        <v>9.0976</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0011</v>
+        <v>6.2873</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6562</v>
+        <v>2.8103</v>
       </c>
       <c r="G2" t="n">
         <v>6.438</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3068</v>
+        <v>0.7472</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6103</v>
+        <v>0.8965</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3034</v>
+        <v>-0.1493</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9026</v>
+        <v>3.158</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2239</v>
+        <v>2.51</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6788</v>
+        <v>0.648</v>
       </c>
       <c r="G3" t="n">
         <v>1.5598</v>
@@ -688,13 +688,13 @@
         <v>0.2175</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7556</v>
+        <v>1.0109</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2966</v>
+        <v>0.5828</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4589</v>
+        <v>0.4281</v>
       </c>
       <c r="V3" t="n">
         <v>0.3698</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7755</v>
+        <v>2.2095</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4169</v>
+        <v>1.9826</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3586</v>
+        <v>0.2269</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8606</v>
+        <v>1.1795</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6143</v>
+        <v>-0.7179</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2463</v>
+        <v>1.8974</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5707</v>
+        <v>0.9358</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9006</v>
+        <v>-0.5991</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6702</v>
+        <v>1.5348</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2899</v>
+        <v>0.2437</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2863</v>
+        <v>-0.1188</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.3626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6099</v>
+        <v>0.7027</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9337</v>
+        <v>0.4819</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6762</v>
+        <v>0.2208</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3048</v>
+        <v>1.7403</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3554</v>
+        <v>1.6241</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0506</v>
+        <v>0.1163</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1795</v>
+        <v>2.4172</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7179</v>
+        <v>-0.7877</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8974</v>
+        <v>3.205</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9358</v>
+        <v>2.988</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5991</v>
+        <v>0.8061</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5348</v>
+        <v>2.1818</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2437</v>
+        <v>-0.5707</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1188</v>
+        <v>-1.5939</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3626</v>
+        <v>1.0231</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.202</v>
+        <v>0.2355</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1454</v>
+        <v>-0.2764</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0566</v>
+        <v>0.5119</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1246</v>
+        <v>1.6178</v>
       </c>
       <c r="E6" t="n">
-        <v>0.885</v>
+        <v>0.6599</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2395</v>
+        <v>0.9579</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4172</v>
+        <v>1.8606</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7877</v>
+        <v>0.6143</v>
       </c>
       <c r="I6" t="n">
-        <v>3.205</v>
+        <v>1.2463</v>
       </c>
       <c r="J6" t="n">
-        <v>2.988</v>
+        <v>1.5707</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8061</v>
+        <v>0.9006</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1818</v>
+        <v>0.6702</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5707</v>
+        <v>0.2899</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5939</v>
+        <v>-0.2863</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0231</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3802</v>
+        <v>0.4521</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0154</v>
+        <v>0.1767</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6352</v>
+        <v>0.2755</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.705</v>
+        <v>0.998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1771</v>
+        <v>0.2699</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8822</v>
+        <v>0.7281</v>
       </c>
       <c r="G7" t="n">
         <v>0.0868</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8358</v>
+        <v>1.1287</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2091</v>
+        <v>0.6561</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6267</v>
+        <v>0.4726</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5681</v>
+        <v>0.6674</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0148</v>
+        <v>-0.9463</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5829</v>
+        <v>1.6137</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3861</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3871</v>
+        <v>0.4864</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3257</v>
+        <v>0.3942</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0614</v>
+        <v>0.0922</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9554</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6644</v>
+        <v>-2.2752</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3231</v>
+        <v>-1.2113</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3413</v>
+        <v>-1.0639</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5189</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5805</v>
+        <v>-0.1914</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.536</v>
+        <v>-0.4242</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0446</v>
+        <v>0.2328</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8938</v>
+        <v>-2.5227</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5764</v>
+        <v>-2.1303</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6825</v>
+        <v>-0.3924</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4937</v>
+        <v>-0.7361</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5964</v>
+        <v>2.0528</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0901</v>
+        <v>-2.789</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4122</v>
+        <v>-0.8076</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0836</v>
+        <v>2.324</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.4958</v>
+        <v>-3.1316</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9185</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4872</v>
+        <v>-0.2712</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4056</v>
+        <v>0.3426</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4041</v>
+        <v>-0.3515</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1202</v>
+        <v>-0.2776</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2839</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.8042</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.1093</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>-1.695</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1799</v>
+        <v>-2.7058</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6025</v>
+        <v>-4.1726</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5773</v>
+        <v>1.4668</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7361</v>
+        <v>-0.4937</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0528</v>
+        <v>1.5964</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.789</v>
+        <v>-2.0901</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8076</v>
+        <v>-1.4122</v>
       </c>
       <c r="K11" t="n">
-        <v>2.324</v>
+        <v>2.0836</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1316</v>
+        <v>-3.4958</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.9185</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2712</v>
+        <v>-0.4872</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3426</v>
+        <v>1.4056</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0087</v>
+        <v>0.5921</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7498</v>
+        <v>0.524</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2589</v>
+        <v>0.0682</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.8042</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>-1.1093</v>
       </c>
       <c r="X11" t="n">
         <v>-1.695</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.2998</v>
+        <v>11.9849</v>
       </c>
       <c r="E12" t="n">
-        <v>4.188400000000001</v>
+        <v>4.8733</v>
       </c>
       <c r="F12" t="n">
-        <v>7.111499999999999</v>
+        <v>7.1117</v>
       </c>
       <c r="G12" t="n">
         <v>11.4071</v>
       </c>
       <c r="H12" t="n">
-        <v>5.792999999999999</v>
+        <v>5.793</v>
       </c>
       <c r="I12" t="n">
         <v>5.613999999999999</v>
@@ -1369,13 +1369,13 @@
         <v>10.7232</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.314499999999999</v>
+        <v>-1.3145</v>
       </c>
       <c r="M12" t="n">
         <v>1.9983</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.930499999999999</v>
+        <v>-4.9305</v>
       </c>
       <c r="O12" t="n">
         <v>6.9285</v>
@@ -1390,13 +1390,13 @@
         <v>13.0502</v>
       </c>
       <c r="S12" t="n">
-        <v>4.127899999999999</v>
+        <v>4.8127</v>
       </c>
       <c r="T12" t="n">
-        <v>2.049</v>
+        <v>2.734</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0788</v>
+        <v>2.0789</v>
       </c>
       <c r="V12" t="n">
         <v>-6.41</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9891</v>
+        <v>2.367</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4133</v>
+        <v>1.4991</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5758</v>
+        <v>0.8679</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3999</v>
+        <v>-2.2232</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8119</v>
+        <v>-3.0957</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5881</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4096</v>
+        <v>-1.8772</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9307</v>
+        <v>-1.9154</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4789</v>
+        <v>0.0382</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0097</v>
+        <v>-0.3461</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1188</v>
+        <v>-1.1803</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1091</v>
+        <v>0.8343</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3032</v>
+        <v>0.4401</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0036</v>
+        <v>0.3137</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3068</v>
+        <v>0.1265</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1952</v>
+        <v>4.1501</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>4.1501</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5809</v>
+        <v>1.5986</v>
       </c>
       <c r="E14" t="n">
-        <v>1.052</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5289</v>
+        <v>0.6323</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2232</v>
+        <v>1.3999</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0957</v>
+        <v>0.8119</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.5881</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.8772</v>
+        <v>1.4096</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9154</v>
+        <v>0.9307</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0382</v>
+        <v>0.4789</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3461</v>
+        <v>-0.0097</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1803</v>
+        <v>-0.1188</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8343</v>
+        <v>0.1091</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.346</v>
+        <v>-0.6937</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1334</v>
+        <v>-0.4434</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2126</v>
+        <v>-0.2503</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1501</v>
+        <v>-0.1952</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1501</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.307</v>
+        <v>1.4573</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2579</v>
+        <v>1.5932</v>
       </c>
       <c r="F15" t="n">
-        <v>0.049</v>
+        <v>-0.1359</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2407</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2877</v>
+        <v>0.438</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3268</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6145</v>
+        <v>0.4296</v>
       </c>
       <c r="V15" t="n">
         <v>1.695</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.181</v>
+        <v>0.2035</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0503</v>
+        <v>1.7897</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8693</v>
+        <v>-1.5861</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9648</v>
+        <v>0.1714</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9002</v>
+        <v>0.2615</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0645</v>
+        <v>-0.0901</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6972</v>
+        <v>1.5111</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6972</v>
+        <v>0.8609</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.6502</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-1.3397</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.5994</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0645</v>
+        <v>-0.7403</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1286</v>
+        <v>0.0544</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3531</v>
+        <v>0.0409</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2245</v>
+        <v>0.0135</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
         <v>-1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0738</v>
+        <v>0.0403</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9014</v>
+        <v>2.1562</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8276</v>
+        <v>-2.1159</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1714</v>
+        <v>0.9648</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2615</v>
+        <v>0.9002</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0901</v>
+        <v>0.0645</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5111</v>
+        <v>1.6972</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8609</v>
+        <v>1.6972</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6502</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3397</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5994</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7403</v>
+        <v>0.0645</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.012</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1526</v>
+        <v>0.4591</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.228</v>
+        <v>-0.4711</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-1.13</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.7074</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1968</v>
+        <v>-1.8615</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3082</v>
+        <v>1.1541</v>
       </c>
       <c r="G18" t="n">
         <v>-0.157</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1014</v>
+        <v>-0.9202</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0959</v>
+        <v>-0.7607</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0054</v>
+        <v>-0.1595</v>
       </c>
       <c r="V18" t="n">
         <v>0.3698</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>P. MONTESDEOCA SANTANA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1708</v>
+        <v>-1.1597</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7789</v>
+        <v>-1.3601</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6082</v>
+        <v>0.2004</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2187</v>
+        <v>-1.0248</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1956</v>
+        <v>0.3163</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9769</v>
+        <v>-1.3411</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.409</v>
+        <v>-1.4719</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4473</v>
+        <v>0.0182</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>-1.4901</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1903</v>
+        <v>0.447</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7484</v>
+        <v>0.298</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9387</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0479</v>
+        <v>-0.1349</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2824</v>
+        <v>0.1118</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3303</v>
+        <v>-0.2466</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MONTESDEOCA SANTANA</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3023</v>
+        <v>-1.3658</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4719</v>
+        <v>-0.1368</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1696</v>
+        <v>-1.2291</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0248</v>
+        <v>-2.5347</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3163</v>
+        <v>-0.3163</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3411</v>
+        <v>-2.2185</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4719</v>
+        <v>-0.732</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0182</v>
+        <v>0.6816</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4901</v>
+        <v>-1.4136</v>
       </c>
       <c r="M20" t="n">
-        <v>0.447</v>
+        <v>-1.8027</v>
       </c>
       <c r="N20" t="n">
-        <v>0.298</v>
+        <v>-0.9978</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2775</v>
+        <v>-0.1139</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2775</v>
+        <v>-0.1235</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. PREPELIC</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6668</v>
+        <v>-1.4251</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3914</v>
+        <v>-3.0025</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7246</v>
+        <v>1.5773</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4766</v>
+        <v>-1.2187</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5181</v>
+        <v>-2.1956</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0415</v>
+        <v>0.9769</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.102</v>
+        <v>-1.409</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1402</v>
+        <v>-1.4473</v>
       </c>
       <c r="L21" t="n">
         <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3747</v>
+        <v>0.1903</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3779</v>
+        <v>-0.7484</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0032</v>
+        <v>0.9387</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.0875</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8974</v>
+        <v>-0.2064</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8857</v>
+        <v>-0.5059</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0118</v>
+        <v>0.2995</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>B. PREPELIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4012</v>
+        <v>-1.9519</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8073</v>
+        <v>-2.6149</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5939</v>
+        <v>0.663</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5347</v>
+        <v>-1.4766</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3163</v>
+        <v>-2.5181</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2185</v>
+        <v>1.0415</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.732</v>
+        <v>-1.102</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6816</v>
+        <v>-1.1402</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4136</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8027</v>
+        <v>-0.3747</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9978</v>
+        <v>-1.3779</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8048999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1492</v>
+        <v>0.6123</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6609</v>
+        <v>0.6621</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4883</v>
+        <v>-0.0499</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8329</v>
+        <v>-3.3448</v>
       </c>
       <c r="E23" t="n">
         <v>-1.0727</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7602</v>
+        <v>-2.2721</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0993</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.211</v>
+        <v>-1.7229</v>
       </c>
       <c r="T23" t="n">
         <v>-1.0154</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1956</v>
+        <v>-0.7075</v>
       </c>
       <c r="V23" t="n">
         <v>1.695</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1692</v>
+        <v>-6.2668</v>
       </c>
       <c r="E24" t="n">
         <v>-5.0675</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1017</v>
+        <v>-1.1993</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9681</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.026</v>
+        <v>-1.1236</v>
       </c>
       <c r="T24" t="n">
         <v>-0.9589</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.1646</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.3</v>
+        <v>-10.5548</v>
       </c>
       <c r="E25" t="n">
         <v>-7.111599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.1884</v>
+        <v>-3.4434</v>
       </c>
       <c r="G25" t="n">
         <v>-11.407</v>
@@ -2380,10 +2380,10 @@
         <v>-1.9982</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9303</v>
+        <v>4.930299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.928700000000001</v>
+        <v>-6.928699999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-9.408999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>10.8751</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.127999999999999</v>
+        <v>-3.3828</v>
       </c>
       <c r="T25" t="n">
         <v>-2.0787</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0492</v>
+        <v>-1.3039</v>
       </c>
       <c r="V25" t="n">
         <v>6.410100000000002</v>
@@ -2419,7 +2419,7 @@
         <v>10.0159</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.6058</v>
+        <v>-3.605799999999999</v>
       </c>
     </row>
   </sheetData>
